--- a/data/trans_dic/P56$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,36</t>
+          <t>0,0; 31,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 10,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 19,84</t>
+          <t>2,39; 19,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 30,65</t>
+          <t>5,92; 31,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,36</t>
+          <t>0,61; 5,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,88</t>
+          <t>0,0; 14,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 15,94</t>
+          <t>1,93; 16,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 20,63</t>
+          <t>3,99; 20,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,71</t>
+          <t>0,9; 5,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,04</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,68</t>
+          <t>0,0; 27,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,44</t>
+          <t>0,0; 15,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,57</t>
+          <t>0,0; 24,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,07</t>
+          <t>1,59; 14,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 33,35</t>
+          <t>5,11; 29,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,06</t>
+          <t>1,86; 8,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 15,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,64</t>
+          <t>1,19; 10,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 24,78</t>
+          <t>5,79; 25,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,07</t>
+          <t>1,79; 8,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,06</t>
+          <t>0,0; 47,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,51</t>
+          <t>0,0; 33,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 51,57</t>
+          <t>4,99; 53,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,6</t>
+          <t>0,0; 22,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,9</t>
+          <t>0,0; 38,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,12</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,65</t>
+          <t>0,0; 15,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,1</t>
+          <t>2,86; 15,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 29,33</t>
+          <t>3,08; 32,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,34</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 23,41</t>
+          <t>3,03; 23,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 12,44</t>
+          <t>2,28; 12,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,46</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 18,46</t>
+          <t>3,26; 17,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 37,97</t>
+          <t>8,45; 38,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 22,54</t>
+          <t>3,82; 20,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 42,22</t>
+          <t>15,82; 42,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,68</t>
+          <t>2,4; 10,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 30,55</t>
+          <t>8,63; 30,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,09</t>
+          <t>2,67; 14,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 34,0</t>
+          <t>11,21; 32,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,9</t>
+          <t>3,74; 10,5</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 16,29</t>
+          <t>1,92; 15,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 18,46</t>
+          <t>2,62; 17,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,49</t>
+          <t>2,72; 9,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,21</t>
+          <t>5,12; 19,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,72</t>
+          <t>3,65; 10,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 23,44</t>
+          <t>10,85; 24,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,63</t>
+          <t>3,03; 6,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 15,49</t>
+          <t>5,49; 14,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,75</t>
+          <t>3,23; 8,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 19,5</t>
+          <t>9,75; 19,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,6</t>
+          <t>3,41; 6,71</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4759</t>
+          <t>0; 4100</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1808</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1569</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2786</t>
+          <t>0; 2600</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1089; 9150</t>
+          <t>1100; 8875</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2418; 12204</t>
+          <t>2358; 12727</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>317; 3315</t>
+          <t>378; 3492</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4682</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>473; 9041</t>
+          <t>1093; 9074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2668; 12126</t>
+          <t>2347; 12313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>981; 4963</t>
+          <t>779; 4688</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5198</t>
+          <t>0; 5072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5593</t>
+          <t>0; 5421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3771</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6724</t>
+          <t>0; 6584</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1054; 9239</t>
+          <t>1045; 9196</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2441; 13696</t>
+          <t>2097; 12278</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>927; 5395</t>
+          <t>1242; 5954</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5304</t>
+          <t>0; 6558</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1120; 10436</t>
+          <t>1166; 10015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3409; 15006</t>
+          <t>3509; 15270</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1600; 7367</t>
+          <t>1634; 7579</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3343</t>
+          <t>0; 3337</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5103</t>
+          <t>0; 4681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>845; 9067</t>
+          <t>878; 9481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6688</t>
+          <t>0; 6823</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5112</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4783</t>
+          <t>0; 5327</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1194; 6376</t>
+          <t>1208; 6492</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>757; 7216</t>
+          <t>758; 8065</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6371</t>
+          <t>0; 6535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1506; 12319</t>
+          <t>1593; 12272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1660; 7777</t>
+          <t>1423; 7828</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2152</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1690</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1013; 5952</t>
+          <t>1051; 5773</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2300; 12203</t>
+          <t>2715; 12292</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2739; 11555</t>
+          <t>1959; 10647</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8972; 23580</t>
+          <t>8839; 23768</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1978; 7750</t>
+          <t>1924; 8574</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3839; 13870</t>
+          <t>3917; 13955</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1969; 10990</t>
+          <t>1941; 10908</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8232; 24447</t>
+          <t>8063; 23040</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3950; 11120</t>
+          <t>4196; 11793</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>928; 7867</t>
+          <t>929; 7709</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 7218</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1821; 13312</t>
+          <t>1886; 12832</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2819; 9681</t>
+          <t>2775; 9954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5358; 18907</t>
+          <t>4787; 18084</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7240; 22002</t>
+          <t>7495; 21985</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17776; 40263</t>
+          <t>18642; 41348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7666; 16643</t>
+          <t>7607; 17087</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7614; 21970</t>
+          <t>7792; 21243</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8668; 24828</t>
+          <t>9166; 24381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24249; 47560</t>
+          <t>23786; 47572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11872; 23313</t>
+          <t>12036; 23709</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,32</t>
+          <t>0,0; 30,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,36</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 19,25</t>
+          <t>2,37; 19,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 31,96</t>
+          <t>7,15; 31,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,65</t>
+          <t>0,54; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,59</t>
+          <t>0,0; 15,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 16,0</t>
+          <t>1,93; 15,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 20,94</t>
+          <t>3,92; 22,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,39</t>
+          <t>1,02; 5,35</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,8</t>
+          <t>0,0; 26,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 20,1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 24,08</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,6; 13,91</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,62; 29,41</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1,4; 8,03</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 15,59</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 24,06</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 14,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,11; 29,9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,86; 8,9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,49</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,21</t>
+          <t>1,22; 11,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 25,21</t>
+          <t>6,06; 25,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,3</t>
+          <t>1,93; 8,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,97</t>
+          <t>0,0; 46,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,49</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 53,93</t>
+          <t>4,77; 51,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,18</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,67</t>
+          <t>0,0; 39,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,75</t>
+          <t>0,0; 12,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,2</t>
+          <t>0,0; 12,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,38</t>
+          <t>3,05; 15,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 32,78</t>
+          <t>3,17; 30,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,63</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 23,32</t>
+          <t>3,31; 24,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 12,52</t>
+          <t>2,85; 12,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,63</t>
+          <t>0,0; 37,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 17,91</t>
+          <t>3,2; 17,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 38,25</t>
+          <t>8,96; 37,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 20,77</t>
+          <t>5,28; 22,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,82; 42,55</t>
+          <t>14,42; 40,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,71</t>
+          <t>2,54; 9,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 30,73</t>
+          <t>8,7; 32,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 14,98</t>
+          <t>2,66; 15,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 32,04</t>
+          <t>11,36; 32,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,5</t>
+          <t>3,4; 9,74</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,97</t>
+          <t>1,93; 16,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 17,8</t>
+          <t>3,2; 16,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,75</t>
+          <t>2,71; 9,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 19,33</t>
+          <t>4,9; 18,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,71</t>
+          <t>3,64; 10,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 24,07</t>
+          <t>11,01; 23,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,81</t>
+          <t>3,12; 6,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,98</t>
+          <t>5,42; 15,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,59</t>
+          <t>3,15; 8,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 19,51</t>
+          <t>9,5; 19,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,71</t>
+          <t>3,41; 6,72</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2257</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4100</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2600</t>
+          <t>0; 2625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1100; 8875</t>
+          <t>1093; 9164</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2358; 12727</t>
+          <t>2847; 12645</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>378; 3492</t>
+          <t>354; 3310</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1093; 9074</t>
+          <t>1095; 9045</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2347; 12313</t>
+          <t>2305; 13250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>779; 4688</t>
+          <t>937; 4917</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4229</t>
         </is>
       </c>
     </row>
@@ -1858,57 +1858,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>0; 5277</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6584</t>
+          <t>0; 6591</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1045; 9196</t>
+          <t>1054; 9135</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2097; 12278</t>
+          <t>2308; 12079</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1242; 5954</t>
+          <t>1038; 5946</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6558</t>
+          <t>0; 6599</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1166; 10015</t>
+          <t>1193; 11418</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3509; 15270</t>
+          <t>3670; 15489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1634; 7579</t>
+          <t>1935; 8514</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4779</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3337</t>
+          <t>0; 3230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4681</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>878; 9481</t>
+          <t>838; 9111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4502</t>
+          <t>0; 3683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6823</t>
+          <t>0; 7005</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4960</t>
+          <t>0; 5164</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5327</t>
+          <t>0; 4409</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1208; 6492</t>
+          <t>1455; 7616</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>758; 8065</t>
+          <t>779; 7505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6535</t>
+          <t>0; 6388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1593; 12272</t>
+          <t>1741; 12703</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1423; 7828</t>
+          <t>2019; 9041</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7378</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2284,47 +2284,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1051; 5773</t>
+          <t>1061; 5894</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2715; 12292</t>
+          <t>2880; 12175</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1959; 10647</t>
+          <t>2705; 11463</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8839; 23768</t>
+          <t>8055; 22846</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1924; 8574</t>
+          <t>2235; 8145</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3917; 13955</t>
+          <t>3953; 14920</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1941; 10908</t>
+          <t>1933; 11373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8063; 23040</t>
+          <t>8169; 23410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4196; 11793</t>
+          <t>4120; 11785</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>929; 7709</t>
+          <t>930; 7811</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7218</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1886; 12832</t>
+          <t>2310; 12109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2775; 9954</t>
+          <t>2947; 10199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4787; 18084</t>
+          <t>4581; 17262</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7495; 21985</t>
+          <t>7468; 22350</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18642; 41348</t>
+          <t>18906; 41034</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7607; 17087</t>
+          <t>8592; 19055</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7792; 21243</t>
+          <t>7687; 21536</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9166; 24381</t>
+          <t>8925; 24093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23786; 47572</t>
+          <t>23168; 47464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12036; 23709</t>
+          <t>13099; 25813</t>
         </is>
       </c>
     </row>
